--- a/AAII_Financials/Yearly/CLPXY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CLPXY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>CLPXY</t>
   </si>
@@ -717,7 +717,7 @@
         <v>4325300</v>
       </c>
       <c r="E8" s="3">
-        <v>5091600</v>
+        <v>4310700</v>
       </c>
       <c r="F8" s="3">
         <v>4178700</v>
@@ -747,10 +747,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2820600</v>
+        <v>149300</v>
       </c>
       <c r="E9" s="3">
-        <v>3180700</v>
+        <v>164600</v>
       </c>
       <c r="F9" s="3">
         <v>149400</v>
@@ -780,10 +780,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1504700</v>
+        <v>4176000</v>
       </c>
       <c r="E10" s="3">
-        <v>1910900</v>
+        <v>4146100</v>
       </c>
       <c r="F10" s="3">
         <v>4029300</v>
@@ -827,11 +827,11 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>20700</v>
-      </c>
-      <c r="E12" s="3">
-        <v>28600</v>
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -894,13 +894,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-9300</v>
+        <v>11600</v>
       </c>
       <c r="E14" s="3">
-        <v>120800</v>
+        <v>142300</v>
       </c>
       <c r="F14" s="3">
-        <v>322500</v>
+        <v>312500</v>
       </c>
       <c r="G14" s="3">
         <v>311500</v>
@@ -927,10 +927,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1817900</v>
+        <v>1849000</v>
       </c>
       <c r="E15" s="3">
-        <v>1593100</v>
+        <v>1588500</v>
       </c>
       <c r="F15" s="3">
         <v>1497800</v>
@@ -972,13 +972,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2847100</v>
+        <v>2797300</v>
       </c>
       <c r="E17" s="3">
-        <v>3191100</v>
+        <v>2441100</v>
       </c>
       <c r="F17" s="3">
-        <v>2231600</v>
+        <v>2241000</v>
       </c>
       <c r="G17" s="3">
         <v>3757800</v>
@@ -1005,13 +1005,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1478200</v>
+        <v>1528000</v>
       </c>
       <c r="E18" s="3">
-        <v>1900400</v>
+        <v>1869600</v>
       </c>
       <c r="F18" s="3">
-        <v>1947100</v>
+        <v>1937700</v>
       </c>
       <c r="G18" s="3">
         <v>2021600</v>
@@ -1053,13 +1053,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>32100</v>
+        <v>20300</v>
       </c>
       <c r="E20" s="3">
-        <v>34400</v>
+        <v>-12500</v>
       </c>
       <c r="F20" s="3">
-        <v>31400</v>
+        <v>32000</v>
       </c>
       <c r="G20" s="3">
         <v>116500</v>
@@ -1086,13 +1086,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3264000</v>
+        <v>3356700</v>
       </c>
       <c r="E21" s="3">
-        <v>3459200</v>
+        <v>3470600</v>
       </c>
       <c r="F21" s="3">
-        <v>3413500</v>
+        <v>3403500</v>
       </c>
       <c r="G21" s="3">
         <v>3392700</v>
@@ -1119,10 +1119,10 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>467100</v>
+        <v>467000</v>
       </c>
       <c r="E22" s="3">
-        <v>479900</v>
+        <v>471300</v>
       </c>
       <c r="F22" s="3">
         <v>482100</v>
@@ -1152,10 +1152,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1017800</v>
+        <v>1038600</v>
       </c>
       <c r="E23" s="3">
-        <v>1404500</v>
+        <v>1284900</v>
       </c>
       <c r="F23" s="3">
         <v>1144800</v>
@@ -1185,10 +1185,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>233200</v>
+        <v>235300</v>
       </c>
       <c r="E24" s="3">
-        <v>267900</v>
+        <v>229700</v>
       </c>
       <c r="F24" s="3">
         <v>198500</v>
@@ -1251,10 +1251,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>784600</v>
+        <v>803300</v>
       </c>
       <c r="E26" s="3">
-        <v>1136600</v>
+        <v>1055200</v>
       </c>
       <c r="F26" s="3">
         <v>946400</v>
@@ -1284,10 +1284,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>647100</v>
+        <v>663100</v>
       </c>
       <c r="E27" s="3">
-        <v>864400</v>
+        <v>875300</v>
       </c>
       <c r="F27" s="3">
         <v>882200</v>
@@ -1353,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>93500</v>
       </c>
       <c r="F29" s="3">
         <v>35800</v>
@@ -1449,13 +1449,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-32100</v>
+        <v>-20300</v>
       </c>
       <c r="E32" s="3">
-        <v>-34400</v>
+        <v>12500</v>
       </c>
       <c r="F32" s="3">
-        <v>-31400</v>
+        <v>-32000</v>
       </c>
       <c r="G32" s="3">
         <v>-116500</v>
@@ -1482,10 +1482,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>647100</v>
+        <v>663100</v>
       </c>
       <c r="E33" s="3">
-        <v>870600</v>
+        <v>881600</v>
       </c>
       <c r="F33" s="3">
         <v>904100</v>
@@ -1548,10 +1548,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>647100</v>
+        <v>663100</v>
       </c>
       <c r="E35" s="3">
-        <v>870600</v>
+        <v>881600</v>
       </c>
       <c r="F35" s="3">
         <v>904100</v>
@@ -1649,10 +1649,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>308600</v>
+        <v>287700</v>
       </c>
       <c r="E41" s="3">
-        <v>453500</v>
+        <v>431800</v>
       </c>
       <c r="F41" s="3">
         <v>678400</v>
@@ -1715,10 +1715,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6534800</v>
+        <v>6350200</v>
       </c>
       <c r="E43" s="3">
-        <v>6193100</v>
+        <v>6021100</v>
       </c>
       <c r="F43" s="3">
         <v>5097800</v>
@@ -1781,10 +1781,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>330300</v>
+        <v>421400</v>
       </c>
       <c r="E45" s="3">
-        <v>372900</v>
+        <v>368400</v>
       </c>
       <c r="F45" s="3">
         <v>460600</v>
@@ -1814,10 +1814,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7283500</v>
+        <v>7143100</v>
       </c>
       <c r="E46" s="3">
-        <v>7118200</v>
+        <v>6906700</v>
       </c>
       <c r="F46" s="3">
         <v>6404300</v>
@@ -1847,10 +1847,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>930400</v>
+        <v>873500</v>
       </c>
       <c r="E47" s="3">
-        <v>884800</v>
+        <v>828500</v>
       </c>
       <c r="F47" s="3">
         <v>878300</v>
@@ -1880,10 +1880,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>27712100</v>
+        <v>28134600</v>
       </c>
       <c r="E48" s="3">
-        <v>25493300</v>
+        <v>25852600</v>
       </c>
       <c r="F48" s="3">
         <v>24706700</v>
@@ -1913,10 +1913,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>862700</v>
+        <v>590600</v>
       </c>
       <c r="E49" s="3">
-        <v>849400</v>
+        <v>615800</v>
       </c>
       <c r="F49" s="3">
         <v>752800</v>
@@ -2012,10 +2012,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>974300</v>
+        <v>1062300</v>
       </c>
       <c r="E52" s="3">
-        <v>797900</v>
+        <v>1012600</v>
       </c>
       <c r="F52" s="3">
         <v>731200</v>
@@ -2078,10 +2078,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>37924700</v>
+        <v>37898500</v>
       </c>
       <c r="E54" s="3">
-        <v>35301500</v>
+        <v>35337200</v>
       </c>
       <c r="F54" s="3">
         <v>33601200</v>
@@ -2141,10 +2141,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2166000</v>
+        <v>659900</v>
       </c>
       <c r="E57" s="3">
-        <v>2523500</v>
+        <v>824200</v>
       </c>
       <c r="F57" s="3">
         <v>1046000</v>
@@ -2174,10 +2174,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8588100</v>
+        <v>8531400</v>
       </c>
       <c r="E58" s="3">
-        <v>6689300</v>
+        <v>7657300</v>
       </c>
       <c r="F58" s="3">
         <v>7048800</v>
@@ -2207,10 +2207,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>721300</v>
+        <v>1871100</v>
       </c>
       <c r="E59" s="3">
-        <v>690500</v>
+        <v>2122000</v>
       </c>
       <c r="F59" s="3">
         <v>1851400</v>
@@ -2240,10 +2240,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>11579700</v>
+        <v>11409400</v>
       </c>
       <c r="E60" s="3">
-        <v>10000200</v>
+        <v>10846500</v>
       </c>
       <c r="F60" s="3">
         <v>10261500</v>
@@ -2273,10 +2273,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>13517400</v>
+        <v>13568400</v>
       </c>
       <c r="E61" s="3">
-        <v>13344500</v>
+        <v>12390700</v>
       </c>
       <c r="F61" s="3">
         <v>11093800</v>
@@ -2306,10 +2306,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>78000</v>
+        <v>156000</v>
       </c>
       <c r="E62" s="3">
-        <v>71700</v>
+        <v>185500</v>
       </c>
       <c r="F62" s="3">
         <v>180900</v>
@@ -2438,10 +2438,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>25238700</v>
+        <v>25256700</v>
       </c>
       <c r="E66" s="3">
-        <v>23473800</v>
+        <v>23551700</v>
       </c>
       <c r="F66" s="3">
         <v>21692400</v>
@@ -2618,10 +2618,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7542500</v>
+        <v>7437200</v>
       </c>
       <c r="E72" s="3">
-        <v>6982900</v>
+        <v>6881700</v>
       </c>
       <c r="F72" s="3">
         <v>6448500</v>
@@ -2750,10 +2750,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>10723300</v>
+        <v>10679600</v>
       </c>
       <c r="E76" s="3">
-        <v>10048300</v>
+        <v>10006600</v>
       </c>
       <c r="F76" s="3">
         <v>10146400</v>
@@ -2854,10 +2854,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>647100</v>
+        <v>663100</v>
       </c>
       <c r="E81" s="3">
-        <v>870600</v>
+        <v>881600</v>
       </c>
       <c r="F81" s="3">
         <v>904100</v>
@@ -2902,10 +2902,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1776900</v>
+        <v>1785600</v>
       </c>
       <c r="E83" s="3">
-        <v>1531900</v>
+        <v>1541000</v>
       </c>
       <c r="F83" s="3">
         <v>1455500</v>
@@ -3295,10 +3295,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>870600</v>
+        <v>391800</v>
       </c>
       <c r="E96" s="3">
-        <v>756700</v>
+        <v>265100</v>
       </c>
       <c r="F96" s="3">
         <v>166100</v>
